--- a/ykk-dsr/hub/tc-out/[Sutrix] DSR -586- [レイアウト] 製品詳細 Overlay化（json2html）・項目fix版連携.xlsx
+++ b/ykk-dsr/hub/tc-out/[Sutrix] DSR -586- [レイアウト] 製品詳細 Overlay化（json2html）・項目fix版連携.xlsx
@@ -1537,7 +1537,7 @@
       </c>
       <c r="U12" s="97" t="inlineStr">
         <is>
-          <t>TD-586-01 seed (QA-PT) – owner Dat</t>
+          <t>TD-586-01 seed (QA-PT) – owner Dat · ver0.4 done ping (Martin)</t>
         </is>
       </c>
       <c r="V12" s="59" t="n"/>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="U14" s="97" t="inlineStr">
         <is>
-          <t>TD-586-01 seed – owner Dat</t>
+          <t>TD-586-01 seed – owner Dat · ver0.4 done ping (Martin)</t>
         </is>
       </c>
       <c r="V14" s="59" t="n"/>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="B28" s="95" t="inlineStr">
         <is>
-          <t>Fixed Product CF field set displayed (項目fix版)</t>
+          <t>ver0.4 display fields shown; removed fields absent</t>
         </is>
       </c>
       <c r="C28" s="95" t="inlineStr">
         <is>
-          <t>EN: Verify every display field of the fixed Product CF set filled in TD-586-01 appears on the page and removed fields do not. JP: 項目fix版の表示項目が表示され、削除項目が表示されないことを確認する。</t>
+          <t>EN: Verify the product detail shows the CF values of the ver0.4 fields the page renders today, and nothing of the 27 removed fields. JP: ver0.4の表示項目がCF値どおり表示され、削除27項目が表示されないことを確認する。</t>
         </is>
       </c>
       <c r="D28" s="95" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="E28" s="95" t="inlineStr">
         <is>
-          <t>EN: 1. Open /ja/products/990586001. 2. For each display field in the fix list, check the value is shown. 3. Check no removed field label appears. JP: 項目ごとに確認。</t>
+          <t>EN: 1. Open /ja/products/990586001. 2. For productName, productCode, description, itemVariations (table), colorVariations, colorVariationsPdf link, notice, printableTape/recycledTape notes: find the TD-586-01 value in the page. 3. Search the page text for removed labels: 生産国, 上下止, スタンダードアイテム, 縫製適正, 外観, 特殊材質, MOQ, オーダーロット, ケアインフォメーション, 納期, 開発会社, 生産会社. JP: TD値を検索、削除項目ラベルを検索。</t>
         </is>
       </c>
       <c r="F28" s="95" t="inlineStr">
         <is>
-          <t>EN: All filled display fields shown with CF values; 0 removed fields shown; list mismatches. JP: 全項目表示、削除項目なし。</t>
+          <t>EN: Every listed TD value that the page renders matches the CF exactly (values not rendered are listed, Pending until design – Q29); 0 removed labels; no literal 'undefined' / 'null'. JP: 表示値一致、削除ラベル0件。</t>
         </is>
       </c>
       <c r="G28" s="95" t="n"/>
@@ -3008,7 +3008,7 @@
       <c r="K28" s="95" t="n"/>
       <c r="L28" s="96" t="inlineStr">
         <is>
-          <t>Scope 'fixed Product CF field set'; DSR-585</t>
+          <t>DSR-585 CR; DM_product_ver0.4; incident 20/10 (dsr-eds#189)</t>
         </is>
       </c>
       <c r="M28" s="96" t="n"/>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="U28" s="97" t="inlineStr">
         <is>
-          <t>DSR-585 項目fix版 not delivered (Q27) – owner Quentin</t>
+          <t>DM_product ver0.4 finished on DEV (Martin done ping – 🔔 P1) + TD-586-01 seed (Night 21/10) – owner Martin/Dat</t>
         </is>
       </c>
       <c r="V28" s="59" t="n"/>
@@ -3241,39 +3241,91 @@
       <c r="AB30" s="59" t="n"/>
     </row>
     <row r="31" ht="187.5" customHeight="1" s="48">
-      <c r="A31" s="84" t="n"/>
-      <c r="B31" s="84" t="n"/>
-      <c r="C31" s="84" t="n"/>
-      <c r="D31" s="84" t="n"/>
-      <c r="E31" s="84" t="n"/>
-      <c r="F31" s="84" t="n"/>
-      <c r="G31" s="84" t="n"/>
-      <c r="H31" s="84" t="inlineStr">
-        <is>
-          <t>To do / 未実施</t>
-        </is>
-      </c>
-      <c r="I31" s="84" t="inlineStr">
-        <is>
-          <t>To do / 未実施</t>
-        </is>
-      </c>
-      <c r="J31" s="84" t="inlineStr">
-        <is>
-          <t>To do / 未実施</t>
-        </is>
-      </c>
-      <c r="K31" s="84" t="n"/>
-      <c r="L31" s="85" t="n"/>
-      <c r="M31" s="86" t="n"/>
-      <c r="N31" s="57" t="n"/>
-      <c r="O31" s="57" t="n"/>
-      <c r="P31" s="87" t="n"/>
-      <c r="Q31" s="87" t="n"/>
-      <c r="R31" s="87" t="n"/>
-      <c r="S31" s="87" t="n"/>
-      <c r="T31" s="87" t="n"/>
-      <c r="U31" s="87" t="n"/>
+      <c r="A31" s="95" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="B31" s="95" t="inlineStr">
+        <is>
+          <t>ver0.4 new fields rendered per design</t>
+        </is>
+      </c>
+      <c r="C31" s="95" t="inlineStr">
+        <is>
+          <t>EN: Verify the ver0.4 new fields (itemVariationsImage, colorVariationsImage, howToUse, howToUseImage, recycledMaterial, recycledMaterialNote, parentProduct, applicableSliderSameAsParent) are rendered on the product detail per design. JP: ver0.4追加項目が設計どおり表示されることを確認する。</t>
+        </is>
+      </c>
+      <c r="D31" s="95" t="inlineStr">
+        <is>
+          <t>EN: DSR-585 model deployed; TD-586-01 filled with all fields. JP: DSR-585反映済み。</t>
+        </is>
+      </c>
+      <c r="E31" s="95" t="inlineStr">
+        <is>
+          <t>EN: 1. Open /ja/products/990586001 (TD-586-01 has all new fields filled). 2. Locate each new field value / image. JP: 追加項目の値・画像を確認。</t>
+        </is>
+      </c>
+      <c r="F31" s="95" t="inlineStr">
+        <is>
+          <t>EN: Each new field shown at the design position with the TD value; images load (naturalWidth &gt; 0). Until a design exists the current state is recorded (expected today: not rendered – incident 20/10). JP: 設計どおり表示。設計なしの間は現状記録。</t>
+        </is>
+      </c>
+      <c r="G31" s="95" t="n"/>
+      <c r="H31" s="95" t="inlineStr">
+        <is>
+          <t>To do / 未実施</t>
+        </is>
+      </c>
+      <c r="I31" s="95" t="inlineStr">
+        <is>
+          <t>To do / 未実施</t>
+        </is>
+      </c>
+      <c r="J31" s="95" t="inlineStr">
+        <is>
+          <t>To do / 未実施</t>
+        </is>
+      </c>
+      <c r="K31" s="95" t="n"/>
+      <c r="L31" s="96" t="inlineStr">
+        <is>
+          <t>差分管理 0.3→0.4 追加; incident 20/10 'parsed but not rendered'</t>
+        </is>
+      </c>
+      <c r="M31" s="96" t="n"/>
+      <c r="N31" s="97" t="n"/>
+      <c r="O31" s="97" t="n"/>
+      <c r="P31" s="97" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="Q31" s="97" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="R31" s="97" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="S31" s="97" t="inlineStr">
+        <is>
+          <t>PC Chromium</t>
+        </is>
+      </c>
+      <c r="T31" s="97" t="inlineStr">
+        <is>
+          <t>TD-586-01</t>
+        </is>
+      </c>
+      <c r="U31" s="97" t="inlineStr">
+        <is>
+          <t>No design for new ver0.4 fields (Figma B04 – Q29) – owner Quentin</t>
+        </is>
+      </c>
       <c r="V31" s="59" t="n"/>
       <c r="W31" s="59" t="n"/>
       <c r="X31" s="59" t="n"/>
@@ -3283,39 +3335,91 @@
       <c r="AB31" s="59" t="n"/>
     </row>
     <row r="32" ht="187.5" customHeight="1" s="48">
-      <c r="A32" s="84" t="n"/>
-      <c r="B32" s="84" t="n"/>
-      <c r="C32" s="84" t="n"/>
-      <c r="D32" s="84" t="n"/>
-      <c r="E32" s="84" t="n"/>
-      <c r="F32" s="84" t="n"/>
-      <c r="G32" s="84" t="n"/>
-      <c r="H32" s="84" t="inlineStr">
-        <is>
-          <t>To do / 未実施</t>
-        </is>
-      </c>
-      <c r="I32" s="84" t="inlineStr">
-        <is>
-          <t>To do / 未実施</t>
-        </is>
-      </c>
-      <c r="J32" s="84" t="inlineStr">
-        <is>
-          <t>To do / 未実施</t>
-        </is>
-      </c>
-      <c r="K32" s="84" t="n"/>
-      <c r="L32" s="85" t="n"/>
-      <c r="M32" s="86" t="n"/>
-      <c r="N32" s="57" t="n"/>
-      <c r="O32" s="57" t="n"/>
-      <c r="P32" s="87" t="n"/>
-      <c r="Q32" s="87" t="n"/>
-      <c r="R32" s="87" t="n"/>
-      <c r="S32" s="87" t="n"/>
-      <c r="T32" s="87" t="n"/>
-      <c r="U32" s="87" t="n"/>
+      <c r="A32" s="95" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="B32" s="95" t="inlineStr">
+        <is>
+          <t>Media slots – media01 first, filled slots only</t>
+        </is>
+      </c>
+      <c r="C32" s="95" t="inlineStr">
+        <is>
+          <t>EN: Verify the product media area shows media01 first and one item per filled slot (media02–15), with no broken item for empty slots. JP: media01が先頭、入力済みスロットのみ表示、空スロットは表示されないことを確認する。</t>
+        </is>
+      </c>
+      <c r="D32" s="95" t="inlineStr">
+        <is>
+          <t>EN: DSR-585 model deployed; TD-586-01 filled with all fields. JP: DSR-585反映済み。</t>
+        </is>
+      </c>
+      <c r="E32" s="95" t="inlineStr">
+        <is>
+          <t>EN: 1. Open /ja/products/990586001 (media01 image, media02 Image, media03 External URL, media04–15 empty). 2. Count media items in the gallery and read the first item src. 3. Check images naturalWidth and failed requests. JP: 件数・先頭・画像読込を確認。</t>
+        </is>
+      </c>
+      <c r="F32" s="95" t="inlineStr">
+        <is>
+          <t>EN: First item = media01Asset; item count = 3 (or 2 + External shown as link – record); 0 images with naturalWidth 0; 0 failed media requests; nothing rendered for media04–15. JP: 先頭media01、3件、壊れ画像0。</t>
+        </is>
+      </c>
+      <c r="G32" s="95" t="n"/>
+      <c r="H32" s="95" t="inlineStr">
+        <is>
+          <t>To do / 未実施</t>
+        </is>
+      </c>
+      <c r="I32" s="95" t="inlineStr">
+        <is>
+          <t>To do / 未実施</t>
+        </is>
+      </c>
+      <c r="J32" s="95" t="inlineStr">
+        <is>
+          <t>To do / 未実施</t>
+        </is>
+      </c>
+      <c r="K32" s="95" t="n"/>
+      <c r="L32" s="96" t="inlineStr">
+        <is>
+          <t>ver0.4 4-2…6-15 (media01 画像固定, Type/Asset/Url)</t>
+        </is>
+      </c>
+      <c r="M32" s="96" t="n"/>
+      <c r="N32" s="97" t="n"/>
+      <c r="O32" s="97" t="n"/>
+      <c r="P32" s="97" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="Q32" s="97" t="inlineStr">
+        <is>
+          <t>Automation</t>
+        </is>
+      </c>
+      <c r="R32" s="97" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="S32" s="97" t="inlineStr">
+        <is>
+          <t>PC Chromium</t>
+        </is>
+      </c>
+      <c r="T32" s="97" t="inlineStr">
+        <is>
+          <t>TD-586-01</t>
+        </is>
+      </c>
+      <c r="U32" s="97" t="inlineStr">
+        <is>
+          <t>DM_product ver0.4 finished on DEV (Martin done ping) + TD-586-01 seed (Night 21/10) · gallery design Q29 – owner Martin/Dat</t>
+        </is>
+      </c>
       <c r="V32" s="59" t="n"/>
       <c r="W32" s="59" t="n"/>
       <c r="X32" s="59" t="n"/>
@@ -5843,10 +5947,26 @@
       </c>
     </row>
     <row r="8" ht="29.25" customHeight="1" s="48">
-      <c r="A8" s="94" t="n"/>
-      <c r="B8" s="94" t="n"/>
-      <c r="C8" s="94" t="n"/>
-      <c r="D8" s="94" t="n"/>
+      <c r="A8" s="98" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="B8" s="98" t="inlineStr">
+        <is>
+          <t>Product model = DM_product_ver0.4 (Drive 1uUgIMKKSL93jjVCQpfTTYtkrFJlAAiSD, Quentin 2026-10-20 comment 61605 on DSR-585): content CF /content/dam/common/{lang}/products/{productId}, CF name = productId digits (no prefix), media01 = image fixed, media02–15 = Type/Asset/Url; 7 required fields. New fields are parsed but not rendered (no design) → 20.0 Blocked; other TCs unchanged.</t>
+        </is>
+      </c>
+      <c r="C8" s="98" t="inlineStr">
+        <is>
+          <t>DSR-585 61605; incident 20/10; BL-OVL-1 update 20/10</t>
+        </is>
+      </c>
+      <c r="D8" s="98" t="inlineStr">
+        <is>
+          <t>TD all, 17.0, 20.0, 21.0</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="48">
       <c r="A9" s="94" t="n"/>
